--- a/artfynd/A 28027-2025 artfynd.xlsx
+++ b/artfynd/A 28027-2025 artfynd.xlsx
@@ -796,42 +796,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125872991</v>
+        <v>125873087</v>
       </c>
       <c r="B3" t="n">
-        <v>98345</v>
+        <v>98324</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515889</v>
+        <v>515902</v>
       </c>
       <c r="R3" t="n">
-        <v>6706868</v>
+        <v>6706785</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -906,42 +906,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125873087</v>
+        <v>125872991</v>
       </c>
       <c r="B4" t="n">
-        <v>98324</v>
+        <v>98345</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -953,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>515902</v>
+        <v>515889</v>
       </c>
       <c r="R4" t="n">
-        <v>6706785</v>
+        <v>6706868</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>

--- a/artfynd/A 28027-2025 artfynd.xlsx
+++ b/artfynd/A 28027-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125690008</v>
       </c>
       <c r="B2" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>125873087</v>
       </c>
       <c r="B3" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>125872991</v>
       </c>
       <c r="B4" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>125873049</v>
       </c>
       <c r="B5" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>125873024</v>
       </c>
       <c r="B6" t="n">
-        <v>98244</v>
+        <v>98251</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>125872902</v>
       </c>
       <c r="B7" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>125872916</v>
       </c>
       <c r="B8" t="n">
-        <v>91671</v>
+        <v>91678</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>125872935</v>
       </c>
       <c r="B9" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>125873065</v>
       </c>
       <c r="B10" t="n">
-        <v>98244</v>
+        <v>98251</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 28027-2025 artfynd.xlsx
+++ b/artfynd/A 28027-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>125873087</v>
       </c>
       <c r="B3" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>125872991</v>
       </c>
       <c r="B4" t="n">
-        <v>98352</v>
+        <v>98353</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>125873049</v>
       </c>
       <c r="B5" t="n">
-        <v>98352</v>
+        <v>98353</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>125873024</v>
       </c>
       <c r="B6" t="n">
-        <v>98251</v>
+        <v>98252</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>125872902</v>
       </c>
       <c r="B7" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>125872916</v>
       </c>
       <c r="B8" t="n">
-        <v>91678</v>
+        <v>91679</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>125872935</v>
       </c>
       <c r="B9" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>125873065</v>
       </c>
       <c r="B10" t="n">
-        <v>98251</v>
+        <v>98252</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 28027-2025 artfynd.xlsx
+++ b/artfynd/A 28027-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125690008</v>
       </c>
       <c r="B2" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,42 +796,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125873087</v>
+        <v>125872991</v>
       </c>
       <c r="B3" t="n">
-        <v>98332</v>
+        <v>98355</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515902</v>
+        <v>515889</v>
       </c>
       <c r="R3" t="n">
-        <v>6706785</v>
+        <v>6706868</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -906,42 +906,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125872991</v>
+        <v>125873087</v>
       </c>
       <c r="B4" t="n">
-        <v>98353</v>
+        <v>98334</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -953,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>515889</v>
+        <v>515902</v>
       </c>
       <c r="R4" t="n">
-        <v>6706868</v>
+        <v>6706785</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1019,7 +1019,7 @@
         <v>125873049</v>
       </c>
       <c r="B5" t="n">
-        <v>98353</v>
+        <v>98355</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>125873024</v>
       </c>
       <c r="B6" t="n">
-        <v>98252</v>
+        <v>98254</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>125872916</v>
       </c>
       <c r="B8" t="n">
-        <v>91679</v>
+        <v>91682</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>125872935</v>
       </c>
       <c r="B9" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>125873065</v>
       </c>
       <c r="B10" t="n">
-        <v>98252</v>
+        <v>98254</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 28027-2025 artfynd.xlsx
+++ b/artfynd/A 28027-2025 artfynd.xlsx
@@ -796,42 +796,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125872991</v>
+        <v>125873087</v>
       </c>
       <c r="B3" t="n">
-        <v>98355</v>
+        <v>98334</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515889</v>
+        <v>515902</v>
       </c>
       <c r="R3" t="n">
-        <v>6706868</v>
+        <v>6706785</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -906,42 +906,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125873087</v>
+        <v>125872991</v>
       </c>
       <c r="B4" t="n">
-        <v>98334</v>
+        <v>98355</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -953,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>515902</v>
+        <v>515889</v>
       </c>
       <c r="R4" t="n">
-        <v>6706785</v>
+        <v>6706868</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>

--- a/artfynd/A 28027-2025 artfynd.xlsx
+++ b/artfynd/A 28027-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125690008</v>
       </c>
       <c r="B2" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,42 +796,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125873087</v>
+        <v>125872991</v>
       </c>
       <c r="B3" t="n">
-        <v>98334</v>
+        <v>98359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515902</v>
+        <v>515889</v>
       </c>
       <c r="R3" t="n">
-        <v>6706785</v>
+        <v>6706868</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -906,42 +906,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125872991</v>
+        <v>125873087</v>
       </c>
       <c r="B4" t="n">
-        <v>98355</v>
+        <v>98338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -953,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>515889</v>
+        <v>515902</v>
       </c>
       <c r="R4" t="n">
-        <v>6706868</v>
+        <v>6706785</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1019,7 +1019,7 @@
         <v>125873049</v>
       </c>
       <c r="B5" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>125873024</v>
       </c>
       <c r="B6" t="n">
-        <v>98254</v>
+        <v>98258</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>125872902</v>
       </c>
       <c r="B7" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>125872916</v>
       </c>
       <c r="B8" t="n">
-        <v>91682</v>
+        <v>91686</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>125872935</v>
       </c>
       <c r="B9" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>125873065</v>
       </c>
       <c r="B10" t="n">
-        <v>98254</v>
+        <v>98258</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 28027-2025 artfynd.xlsx
+++ b/artfynd/A 28027-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125690008</v>
       </c>
       <c r="B2" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,42 +796,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125872991</v>
+        <v>125873087</v>
       </c>
       <c r="B3" t="n">
-        <v>98359</v>
+        <v>98339</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515889</v>
+        <v>515902</v>
       </c>
       <c r="R3" t="n">
-        <v>6706868</v>
+        <v>6706785</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -906,42 +906,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125873087</v>
+        <v>125872991</v>
       </c>
       <c r="B4" t="n">
-        <v>98338</v>
+        <v>98360</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -953,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>515902</v>
+        <v>515889</v>
       </c>
       <c r="R4" t="n">
-        <v>6706785</v>
+        <v>6706868</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1019,7 +1019,7 @@
         <v>125873049</v>
       </c>
       <c r="B5" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>125873024</v>
       </c>
       <c r="B6" t="n">
-        <v>98258</v>
+        <v>98259</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>125872935</v>
       </c>
       <c r="B9" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>125873065</v>
       </c>
       <c r="B10" t="n">
-        <v>98258</v>
+        <v>98259</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 28027-2025 artfynd.xlsx
+++ b/artfynd/A 28027-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125690008</v>
       </c>
       <c r="B2" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>125873087</v>
       </c>
       <c r="B3" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>125872991</v>
       </c>
       <c r="B4" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>125873049</v>
       </c>
       <c r="B5" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>125873024</v>
       </c>
       <c r="B6" t="n">
-        <v>98259</v>
+        <v>98261</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>125872902</v>
       </c>
       <c r="B7" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>125872916</v>
       </c>
       <c r="B8" t="n">
-        <v>91686</v>
+        <v>91688</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>125872935</v>
       </c>
       <c r="B9" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>125873065</v>
       </c>
       <c r="B10" t="n">
-        <v>98259</v>
+        <v>98261</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 28027-2025 artfynd.xlsx
+++ b/artfynd/A 28027-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125690008</v>
       </c>
       <c r="B2" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>125873087</v>
       </c>
       <c r="B3" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>125872991</v>
       </c>
       <c r="B4" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>125873049</v>
       </c>
       <c r="B5" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>125873024</v>
       </c>
       <c r="B6" t="n">
-        <v>98261</v>
+        <v>98263</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>125872902</v>
       </c>
       <c r="B7" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>125872916</v>
       </c>
       <c r="B8" t="n">
-        <v>91688</v>
+        <v>91690</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>125872935</v>
       </c>
       <c r="B9" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>125873065</v>
       </c>
       <c r="B10" t="n">
-        <v>98261</v>
+        <v>98263</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 28027-2025 artfynd.xlsx
+++ b/artfynd/A 28027-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125690008</v>
       </c>
       <c r="B2" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>125873087</v>
       </c>
       <c r="B3" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>125872991</v>
       </c>
       <c r="B4" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>125873049</v>
       </c>
       <c r="B5" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>125873024</v>
       </c>
       <c r="B6" t="n">
-        <v>98263</v>
+        <v>98265</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>125872902</v>
       </c>
       <c r="B7" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>125872916</v>
       </c>
       <c r="B8" t="n">
-        <v>91690</v>
+        <v>91692</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>125872935</v>
       </c>
       <c r="B9" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>125873065</v>
       </c>
       <c r="B10" t="n">
-        <v>98263</v>
+        <v>98265</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 28027-2025 artfynd.xlsx
+++ b/artfynd/A 28027-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125690008</v>
       </c>
       <c r="B2" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,42 +796,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125873087</v>
+        <v>125872991</v>
       </c>
       <c r="B3" t="n">
-        <v>98345</v>
+        <v>98370</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515902</v>
+        <v>515889</v>
       </c>
       <c r="R3" t="n">
-        <v>6706785</v>
+        <v>6706868</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -906,42 +906,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125872991</v>
+        <v>125873087</v>
       </c>
       <c r="B4" t="n">
-        <v>98366</v>
+        <v>98349</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -953,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>515889</v>
+        <v>515902</v>
       </c>
       <c r="R4" t="n">
-        <v>6706868</v>
+        <v>6706785</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1019,7 +1019,7 @@
         <v>125873049</v>
       </c>
       <c r="B5" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>125873024</v>
       </c>
       <c r="B6" t="n">
-        <v>98265</v>
+        <v>98269</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>125872902</v>
       </c>
       <c r="B7" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>125872916</v>
       </c>
       <c r="B8" t="n">
-        <v>91692</v>
+        <v>91696</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>125872935</v>
       </c>
       <c r="B9" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>125873065</v>
       </c>
       <c r="B10" t="n">
-        <v>98265</v>
+        <v>98269</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 28027-2025 artfynd.xlsx
+++ b/artfynd/A 28027-2025 artfynd.xlsx
@@ -796,42 +796,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125872991</v>
+        <v>125873087</v>
       </c>
       <c r="B3" t="n">
-        <v>98370</v>
+        <v>98349</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515889</v>
+        <v>515902</v>
       </c>
       <c r="R3" t="n">
-        <v>6706868</v>
+        <v>6706785</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -906,42 +906,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125873087</v>
+        <v>125872991</v>
       </c>
       <c r="B4" t="n">
-        <v>98349</v>
+        <v>98370</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -953,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>515902</v>
+        <v>515889</v>
       </c>
       <c r="R4" t="n">
-        <v>6706785</v>
+        <v>6706868</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>

--- a/artfynd/A 28027-2025 artfynd.xlsx
+++ b/artfynd/A 28027-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125690008</v>
       </c>
       <c r="B2" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>125873087</v>
       </c>
       <c r="B3" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>125872991</v>
       </c>
       <c r="B4" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>125873049</v>
       </c>
       <c r="B5" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>125873024</v>
       </c>
       <c r="B6" t="n">
-        <v>98269</v>
+        <v>98272</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>125872935</v>
       </c>
       <c r="B9" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>125873065</v>
       </c>
       <c r="B10" t="n">
-        <v>98269</v>
+        <v>98272</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 28027-2025 artfynd.xlsx
+++ b/artfynd/A 28027-2025 artfynd.xlsx
@@ -796,42 +796,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125873087</v>
+        <v>125872991</v>
       </c>
       <c r="B3" t="n">
-        <v>98352</v>
+        <v>98373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515902</v>
+        <v>515889</v>
       </c>
       <c r="R3" t="n">
-        <v>6706785</v>
+        <v>6706868</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -906,42 +906,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125872991</v>
+        <v>125873087</v>
       </c>
       <c r="B4" t="n">
-        <v>98373</v>
+        <v>98352</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -953,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>515889</v>
+        <v>515902</v>
       </c>
       <c r="R4" t="n">
-        <v>6706868</v>
+        <v>6706785</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>

--- a/artfynd/A 28027-2025 artfynd.xlsx
+++ b/artfynd/A 28027-2025 artfynd.xlsx
@@ -796,42 +796,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125872991</v>
+        <v>125873087</v>
       </c>
       <c r="B3" t="n">
-        <v>98373</v>
+        <v>98352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515889</v>
+        <v>515902</v>
       </c>
       <c r="R3" t="n">
-        <v>6706868</v>
+        <v>6706785</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -906,42 +906,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125873087</v>
+        <v>125872991</v>
       </c>
       <c r="B4" t="n">
-        <v>98352</v>
+        <v>98373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -953,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>515902</v>
+        <v>515889</v>
       </c>
       <c r="R4" t="n">
-        <v>6706785</v>
+        <v>6706868</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>

--- a/artfynd/A 28027-2025 artfynd.xlsx
+++ b/artfynd/A 28027-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>125873087</v>
       </c>
       <c r="B3" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>125872991</v>
       </c>
       <c r="B4" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>125873049</v>
       </c>
       <c r="B5" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>125873024</v>
       </c>
       <c r="B6" t="n">
-        <v>98272</v>
+        <v>98281</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>125872902</v>
       </c>
       <c r="B7" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>125872916</v>
       </c>
       <c r="B8" t="n">
-        <v>91696</v>
+        <v>91699</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>125872935</v>
       </c>
       <c r="B9" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>125873065</v>
       </c>
       <c r="B10" t="n">
-        <v>98272</v>
+        <v>98281</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 28027-2025 artfynd.xlsx
+++ b/artfynd/A 28027-2025 artfynd.xlsx
@@ -796,42 +796,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125873087</v>
+        <v>125872991</v>
       </c>
       <c r="B3" t="n">
-        <v>98361</v>
+        <v>98382</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515902</v>
+        <v>515889</v>
       </c>
       <c r="R3" t="n">
-        <v>6706785</v>
+        <v>6706868</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -906,42 +906,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125872991</v>
+        <v>125873087</v>
       </c>
       <c r="B4" t="n">
-        <v>98382</v>
+        <v>98361</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -953,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>515889</v>
+        <v>515902</v>
       </c>
       <c r="R4" t="n">
-        <v>6706868</v>
+        <v>6706785</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>

--- a/artfynd/A 28027-2025 artfynd.xlsx
+++ b/artfynd/A 28027-2025 artfynd.xlsx
@@ -1653,7 +1653,7 @@
         <v>130170034</v>
       </c>
       <c r="B11" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 28027-2025 artfynd.xlsx
+++ b/artfynd/A 28027-2025 artfynd.xlsx
@@ -1653,7 +1653,7 @@
         <v>130170034</v>
       </c>
       <c r="B11" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 28027-2025 artfynd.xlsx
+++ b/artfynd/A 28027-2025 artfynd.xlsx
@@ -1653,7 +1653,7 @@
         <v>130170034</v>
       </c>
       <c r="B11" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 28027-2025 artfynd.xlsx
+++ b/artfynd/A 28027-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1758,6 +1758,226 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>131758033</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57896</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Åkersmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>515935</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6706878</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Födosökshack nedtill död äldre gran.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>131758063</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Åkersmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>515912</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6706923</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28027-2025 artfynd.xlsx
+++ b/artfynd/A 28027-2025 artfynd.xlsx
@@ -1763,7 +1763,7 @@
         <v>131758033</v>
       </c>
       <c r="B12" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>131758063</v>
       </c>
       <c r="B13" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 28027-2025 artfynd.xlsx
+++ b/artfynd/A 28027-2025 artfynd.xlsx
@@ -1763,7 +1763,7 @@
         <v>131758033</v>
       </c>
       <c r="B12" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>131758063</v>
       </c>
       <c r="B13" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 28027-2025 artfynd.xlsx
+++ b/artfynd/A 28027-2025 artfynd.xlsx
@@ -1873,7 +1873,7 @@
         <v>131758063</v>
       </c>
       <c r="B13" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 28027-2025 artfynd.xlsx
+++ b/artfynd/A 28027-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,62 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125690008</v>
+        <v>125872902</v>
       </c>
       <c r="B2" t="n">
-        <v>98352</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Åkersmyra fäbodar, Åkersmyra fäbodar, Dlr</t>
+          <t>Åkersmyran, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>515967</v>
+        <v>515847</v>
       </c>
       <c r="R2" t="n">
-        <v>6706889</v>
+        <v>6706930</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,22 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>15:06</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:06</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,64 +757,56 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Maria Warg</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Maria Warg</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125872991</v>
+        <v>125872916</v>
       </c>
       <c r="B3" t="n">
-        <v>98382</v>
+        <v>92369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -843,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515889</v>
+        <v>515849</v>
       </c>
       <c r="R3" t="n">
-        <v>6706868</v>
+        <v>6706914</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -906,46 +877,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125873087</v>
+        <v>131758033</v>
       </c>
       <c r="B4" t="n">
-        <v>98361</v>
+        <v>57972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -953,13 +920,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>515902</v>
+        <v>515935</v>
       </c>
       <c r="R4" t="n">
-        <v>6706785</v>
+        <v>6706878</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,12 +950,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Födosökshack nedtill död äldre gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -997,7 +969,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1016,60 +987,64 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125873049</v>
+        <v>132419626</v>
       </c>
       <c r="B5" t="n">
-        <v>98382</v>
+        <v>57975</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Åkersmyran, Dlr</t>
+          <t>Åkersmyra Fäbod, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>515922</v>
+        <v>515940</v>
       </c>
       <c r="R5" t="n">
-        <v>6706852</v>
+        <v>6706893</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1093,12 +1068,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Hona och hane som födosöker tillsammans, Honan troligen samma som rapportören såg strax innan.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1107,7 +1087,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1126,33 +1105,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125873024</v>
+        <v>125872935</v>
       </c>
       <c r="B6" t="n">
-        <v>98281</v>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>223597</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1169,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>515881</v>
+        <v>515867</v>
       </c>
       <c r="R6" t="n">
-        <v>6706865</v>
+        <v>6706879</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1232,37 +1215,46 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125872902</v>
+        <v>125873087</v>
       </c>
       <c r="B7" t="n">
-        <v>91245</v>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1270,10 +1262,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>515847</v>
+        <v>515902</v>
       </c>
       <c r="R7" t="n">
-        <v>6706930</v>
+        <v>6706785</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1333,10 +1325,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125872916</v>
+        <v>131758063</v>
       </c>
       <c r="B8" t="n">
-        <v>91699</v>
+        <v>99195</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1344,26 +1336,35 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1371,13 +1372,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>515849</v>
+        <v>515912</v>
       </c>
       <c r="R8" t="n">
-        <v>6706914</v>
+        <v>6706923</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1401,12 +1402,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,42 +1435,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125872935</v>
+        <v>125872991</v>
       </c>
       <c r="B9" t="n">
-        <v>98361</v>
+        <v>99140</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1481,10 +1482,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>515867</v>
+        <v>515889</v>
       </c>
       <c r="R9" t="n">
-        <v>6706879</v>
+        <v>6706868</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1544,10 +1545,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125873065</v>
+        <v>125873049</v>
       </c>
       <c r="B10" t="n">
-        <v>98281</v>
+        <v>99140</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1555,27 +1556,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>223597</v>
+        <v>221952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1587,10 +1592,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>515924</v>
+        <v>515922</v>
       </c>
       <c r="R10" t="n">
-        <v>6706847</v>
+        <v>6706852</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1650,56 +1655,56 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130170034</v>
+        <v>125873024</v>
       </c>
       <c r="B11" t="n">
-        <v>57854</v>
+        <v>99038</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>223597</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Åkersmyra Fäbodar, Dlr</t>
+          <t>Åkersmyran, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>515970</v>
+        <v>515881</v>
       </c>
       <c r="R11" t="n">
-        <v>6706894</v>
+        <v>6706865</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1723,17 +1728,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1742,6 +1742,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1760,42 +1761,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131758033</v>
+        <v>125873065</v>
       </c>
       <c r="B12" t="n">
-        <v>57945</v>
+        <v>99038</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>223597</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1803,13 +1804,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>515935</v>
+        <v>515924</v>
       </c>
       <c r="R12" t="n">
-        <v>6706878</v>
+        <v>6706847</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1833,17 +1834,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Födosökshack nedtill död äldre gran.</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,6 +1848,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1870,57 +1867,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131758063</v>
+        <v>130170617</v>
       </c>
       <c r="B13" t="n">
-        <v>99098</v>
+        <v>91872</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Åkersmyran, Dlr</t>
+          <t>Åkersmyra Fäbodar, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>515912</v>
+        <v>516118</v>
       </c>
       <c r="R13" t="n">
-        <v>6706923</v>
+        <v>6706602</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1947,12 +1935,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1980,27 +1968,27 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132419664</v>
+        <v>132419693</v>
       </c>
       <c r="B14" t="n">
-        <v>57957</v>
+        <v>57972</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2008,20 +1996,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2031,10 +2011,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>515961</v>
+        <v>515969</v>
       </c>
       <c r="R14" t="n">
-        <v>6706780</v>
+        <v>6706748</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2071,7 +2051,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Födosöker i död gran.</t>
+          <t>Födosökshack nedtill dött barrträd.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2098,27 +2078,27 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132419626</v>
+        <v>132712292</v>
       </c>
       <c r="B15" t="n">
-        <v>57957</v>
+        <v>57972</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2126,36 +2106,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Åkersmyra Fäbod, Dlr</t>
+          <t>Åkersmyra, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>515940</v>
+        <v>515989</v>
       </c>
       <c r="R15" t="n">
-        <v>6706893</v>
+        <v>6706728</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2179,17 +2151,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Hona och hane som födosöker tillsammans, Honan troligen samma som rapportören såg strax innan.</t>
+          <t>Födosökshack nedtill på tall.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2216,10 +2188,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132419693</v>
+        <v>125689777</v>
       </c>
       <c r="B16" t="n">
-        <v>57954</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2227,16 +2199,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2245,27 +2217,24 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Åkersmyra Fäbod, Dlr</t>
+          <t>Åkersmyra fäbodar, Åkersmyra fäbodar, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>515969</v>
+        <v>515978</v>
       </c>
       <c r="R16" t="n">
-        <v>6706748</v>
+        <v>6706876</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2289,17 +2258,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Födosökshack nedtill dött barrträd.</t>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2310,48 +2284,53 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Maria Warg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Maria Warg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132712175</v>
+        <v>130170034</v>
       </c>
       <c r="B17" t="n">
-        <v>57145</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2359,20 +2338,20 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Åkersmyra, Dlr</t>
+          <t>Åkersmyra Fäbodar, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>516040</v>
+        <v>515970</v>
       </c>
       <c r="R17" t="n">
-        <v>6706652</v>
+        <v>6706894</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2399,12 +2378,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2025-12-17</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2431,10 +2415,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132712292</v>
+        <v>130255133</v>
       </c>
       <c r="B18" t="n">
-        <v>57955</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2442,16 +2426,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2464,23 +2448,23 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Åkersmyra, Dlr</t>
+          <t>Åkersmyra naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>515989</v>
+        <v>515993</v>
       </c>
       <c r="R18" t="n">
-        <v>6706728</v>
+        <v>6706801</v>
       </c>
       <c r="S18" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2504,17 +2488,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Födosökshack nedtill på tall.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2538,6 +2522,581 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>130255150</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Åkersmyra naturreservat., Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>516010</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6706789</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>132419664</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Åkersmyra Fäbod, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>515961</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6706780</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Födosöker i död gran.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>132712175</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Åkersmyra, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>516040</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6706652</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>125689956</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Åkersmyra fäbodar, Åkersmyra fäbodar, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>515978</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6706876</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Maria Warg</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Maria Warg</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>125690008</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Åkersmyra fäbodar, Åkersmyra fäbodar, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>515967</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6706889</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Maria Warg</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Maria Warg</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28027-2025 artfynd.xlsx
+++ b/artfynd/A 28027-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125872902</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125872916</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130170617</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1085,6 +1105,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131758033</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1195,6 +1220,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132419693</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1305,6 +1335,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132712292</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1422,6 +1457,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125689777</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1532,6 +1572,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130170034</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1642,6 +1687,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130255133</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1752,6 +1802,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130255150</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1870,6 +1925,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132419626</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1988,6 +2048,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132419664</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2093,6 +2158,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132712175</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2214,6 +2284,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125689956</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2335,6 +2410,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125690008</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2445,6 +2525,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125872935</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2555,6 +2640,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125873087</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2665,6 +2755,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131758063</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2775,6 +2870,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125872991</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2885,6 +2985,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125873049</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2991,6 +3096,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125873024</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3097,8 +3207,37 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125873065</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>